--- a/apps/web/server/modules/inquiry/excelTemplate/inquiry.xlsx
+++ b/apps/web/server/modules/inquiry/excelTemplate/inquiry.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="94" uniqueCount="84">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="95" uniqueCount="85">
   <si>
     <t>EXPORTER:</t>
   </si>
@@ -44,6 +44,9 @@
     <t xml:space="preserve">ADDR： </t>
   </si>
   <si>
+    <t>{{exporterAddr}}</t>
+  </si>
+  <si>
     <t>web</t>
   </si>
   <si>
@@ -179,7 +182,25 @@
     <t>REMARK</t>
   </si>
   <si>
-    <t>{{termsCode1}}</t>
+    <r>
+      <t>{{</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="微软雅黑"/>
+        <charset val="134"/>
+      </rPr>
+      <t>termsCode1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="微软雅黑"/>
+        <charset val="134"/>
+      </rPr>
+      <t>}}</t>
+    </r>
   </si>
   <si>
     <t>{{termsDesc1}}</t>
@@ -293,7 +314,7 @@
     <numFmt numFmtId="176" formatCode="[$-409]dd/mmm/yy;@"/>
     <numFmt numFmtId="177" formatCode="0.000_);[Red]\(0.000\)"/>
   </numFmts>
-  <fonts count="40">
+  <fonts count="42">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -393,6 +414,11 @@
     </font>
     <font>
       <sz val="12"/>
+      <name val="微软雅黑"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <name val="微软雅黑"/>
       <charset val="134"/>
     </font>
@@ -566,6 +592,11 @@
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="10"/>
+      <name val="微软雅黑"/>
+      <charset val="134"/>
+    </font>
   </fonts>
   <fills count="34">
     <fill>
@@ -1563,133 +1594,133 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="55" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="25" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="56" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="27" fillId="0" borderId="56" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="57" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="6" borderId="58" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="7" borderId="59" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="7" borderId="58" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="8" borderId="60" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="0" borderId="61" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="34" fillId="0" borderId="62" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="35" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="37" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="38" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="38" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="38" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="38" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="38" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="38" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="38" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="38" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="38" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="38" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="38" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="38" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="56" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="57" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="6" borderId="58" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="7" borderId="59" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="7" borderId="58" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="8" borderId="60" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="61" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="0" borderId="62" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="40" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="40" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="40" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="40" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="40" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="40" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="40" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="40" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="40" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="40" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="40" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="40" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1897,7 +1928,7 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="37" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="3" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1997,37 +2028,37 @@
     <xf numFmtId="0" fontId="15" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="48" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -2036,22 +2067,22 @@
     <xf numFmtId="0" fontId="13" fillId="0" borderId="50" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="51" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="51" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="52" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="52" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="53" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="53" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="54" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -2449,7 +2480,9 @@
       <c r="B2" s="9" t="s">
         <v>4</v>
       </c>
-      <c r="C2" s="10"/>
+      <c r="C2" s="10" t="s">
+        <v>5</v>
+      </c>
       <c r="D2" s="10"/>
       <c r="E2" s="11"/>
       <c r="F2" s="10"/>
@@ -2463,38 +2496,38 @@
     <row r="3" ht="22.5" customHeight="1" spans="1:13">
       <c r="A3" s="15"/>
       <c r="B3" s="16" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C3" s="17" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D3" s="18"/>
       <c r="E3" s="19" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F3" s="20" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G3" s="18"/>
       <c r="H3" s="21"/>
       <c r="I3" s="18" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J3" s="22" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K3" s="23"/>
       <c r="L3" s="24"/>
     </row>
-    <row r="4" ht="22.5" customHeight="1" spans="1:13">
+    <row r="4" ht="18.75" spans="1:13">
       <c r="A4" s="25" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B4" s="26" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C4" s="27" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D4" s="27"/>
       <c r="E4" s="27"/>
@@ -2502,25 +2535,25 @@
       <c r="G4" s="27"/>
       <c r="H4" s="28"/>
       <c r="I4" s="27" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J4" s="29" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K4" s="30" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="L4" s="31" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
-    <row r="5" ht="22.5" customHeight="1" spans="1:13">
+    <row r="5" ht="18" spans="1:13">
       <c r="A5" s="32"/>
       <c r="B5" s="33" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C5" s="34" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D5" s="34"/>
       <c r="E5" s="34"/>
@@ -2528,25 +2561,25 @@
       <c r="G5" s="34"/>
       <c r="H5" s="35"/>
       <c r="I5" s="34" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J5" s="36" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K5" s="37" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="L5" s="38" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
-    <row r="6" ht="22.5" customHeight="1" spans="1:13">
+    <row r="6" ht="18" spans="1:13">
       <c r="A6" s="32"/>
       <c r="B6" s="39" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C6" s="10" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D6" s="10"/>
       <c r="E6" s="10"/>
@@ -2554,23 +2587,23 @@
       <c r="G6" s="10"/>
       <c r="H6" s="40"/>
       <c r="I6" s="34" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J6" s="36" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="K6" s="37" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="L6" s="38"/>
     </row>
-    <row r="7" ht="22.5" customHeight="1" spans="1:13">
+    <row r="7" ht="18.75" spans="1:13">
       <c r="A7" s="41"/>
       <c r="B7" s="16" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C7" s="17" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D7" s="18"/>
       <c r="E7" s="18"/>
@@ -2578,26 +2611,26 @@
       <c r="G7" s="18"/>
       <c r="H7" s="21"/>
       <c r="I7" s="42" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J7" s="43" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="K7" s="44" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="L7" s="45"/>
     </row>
-    <row r="8" ht="22.5" customHeight="1" spans="1:13">
+    <row r="8" ht="18.75" spans="1:13">
       <c r="A8" s="46" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B8" s="47" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C8" s="48"/>
       <c r="D8" s="49" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E8" s="50"/>
       <c r="F8" s="50"/>
@@ -2606,64 +2639,64 @@
       <c r="I8" s="50"/>
       <c r="J8" s="51"/>
       <c r="K8" s="52" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="L8" s="53"/>
     </row>
-    <row r="9" ht="23.25" customHeight="1" spans="1:13">
+    <row r="9" ht="17.25" spans="1:13">
       <c r="A9" s="54"/>
       <c r="B9" s="55" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C9" s="56"/>
       <c r="D9" s="57" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E9" s="57"/>
       <c r="F9" s="57"/>
       <c r="G9" s="57"/>
       <c r="H9" s="10" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="I9" s="57" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="J9" s="58"/>
       <c r="K9" s="59" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="L9" s="60"/>
     </row>
-    <row r="10" ht="22.5" customHeight="1" spans="1:13">
+    <row r="10" ht="17.25" spans="1:13">
       <c r="A10" s="54"/>
       <c r="B10" s="55" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C10" s="56"/>
       <c r="D10" s="57" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="E10" s="57"/>
       <c r="F10" s="57"/>
       <c r="G10" s="57"/>
       <c r="H10" s="10" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="I10" s="57" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="J10" s="58"/>
       <c r="K10" s="61"/>
       <c r="L10" s="62"/>
     </row>
-    <row r="11" ht="22.5" customHeight="1" spans="1:13">
+    <row r="11" ht="18" spans="1:13">
       <c r="A11" s="63"/>
       <c r="B11" s="64" t="s">
         <v>4</v>
       </c>
       <c r="C11" s="65"/>
       <c r="D11" s="66" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E11" s="66"/>
       <c r="F11" s="66"/>
@@ -2675,54 +2708,54 @@
       <c r="L11" s="62"/>
       <c r="M11" s="68"/>
     </row>
-    <row r="12" ht="22.5" customHeight="1" spans="1:13">
+    <row r="12" ht="18" spans="1:13">
       <c r="A12" s="46" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B12" s="69" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C12" s="70" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D12" s="71"/>
       <c r="E12" s="71"/>
       <c r="F12" s="72"/>
       <c r="G12" s="73" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H12" s="74" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="I12" s="75" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="J12" s="76" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="K12" s="61"/>
       <c r="L12" s="62"/>
     </row>
-    <row r="13" ht="22.5" customHeight="1" spans="1:13">
+    <row r="13" ht="51.75" spans="1:13">
       <c r="A13" s="54"/>
       <c r="B13" s="77" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C13" s="78" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D13" s="79"/>
       <c r="E13" s="79"/>
       <c r="F13" s="80"/>
       <c r="G13" s="81" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="H13" s="82"/>
       <c r="I13" s="81" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="J13" s="83" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="K13" s="61"/>
       <c r="L13" s="62"/>
@@ -2735,11 +2768,11 @@
       <c r="E14" s="84"/>
       <c r="F14" s="84"/>
       <c r="G14" s="85" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="H14" s="85"/>
       <c r="I14" s="86" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="J14" s="87"/>
       <c r="K14" s="61"/>
@@ -2747,14 +2780,14 @@
     </row>
     <row r="15" ht="39.75" customHeight="1" spans="1:13">
       <c r="A15" s="46" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B15" s="88" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C15" s="89"/>
       <c r="D15" s="90" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E15" s="90"/>
       <c r="F15" s="90"/>
@@ -2768,11 +2801,11 @@
     <row r="16" ht="22.5" customHeight="1" spans="1:13">
       <c r="A16" s="54"/>
       <c r="B16" s="92" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C16" s="93"/>
       <c r="D16" s="94" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E16" s="94"/>
       <c r="F16" s="94"/>
@@ -2786,11 +2819,11 @@
     <row r="17" ht="22.5" customHeight="1" spans="1:13">
       <c r="A17" s="54"/>
       <c r="B17" s="92" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C17" s="93"/>
       <c r="D17" s="94" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="E17" s="94"/>
       <c r="F17" s="94"/>
@@ -2802,14 +2835,14 @@
       <c r="L17" s="62"/>
       <c r="M17" s="96"/>
     </row>
-    <row r="18" ht="22.5" customHeight="1" spans="1:13">
+    <row r="18" ht="26" customHeight="1" spans="1:13">
       <c r="A18" s="54"/>
       <c r="B18" s="92" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C18" s="93"/>
       <c r="D18" s="94" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="E18" s="94"/>
       <c r="F18" s="94"/>
@@ -2823,11 +2856,11 @@
     <row r="19" ht="34.5" customHeight="1" spans="1:13">
       <c r="A19" s="63"/>
       <c r="B19" s="97" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C19" s="98"/>
       <c r="D19" s="99" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="E19" s="99"/>
       <c r="F19" s="99"/>
@@ -2841,14 +2874,14 @@
     </row>
     <row r="20" ht="22.5" customHeight="1" spans="1:13">
       <c r="A20" s="46" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B20" s="88" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C20" s="89"/>
       <c r="D20" s="34" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E20" s="34"/>
       <c r="F20" s="34"/>
@@ -2862,11 +2895,11 @@
     <row r="21" ht="22.5" customHeight="1" spans="1:13">
       <c r="A21" s="54"/>
       <c r="B21" s="92" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C21" s="93"/>
       <c r="D21" s="94" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="E21" s="94"/>
       <c r="F21" s="94"/>
@@ -2880,11 +2913,11 @@
     <row r="22" ht="22.5" customHeight="1" spans="1:13">
       <c r="A22" s="54"/>
       <c r="B22" s="92" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C22" s="93"/>
       <c r="D22" s="94" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="E22" s="94"/>
       <c r="F22" s="94"/>
@@ -2898,11 +2931,11 @@
     <row r="23" ht="22.5" customHeight="1" spans="1:13">
       <c r="A23" s="63"/>
       <c r="B23" s="102" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C23" s="98"/>
       <c r="D23" s="99" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="E23" s="99"/>
       <c r="F23" s="99"/>
@@ -2913,22 +2946,22 @@
       <c r="K23" s="61"/>
       <c r="L23" s="62"/>
     </row>
-    <row r="24" ht="22.5" customHeight="1" spans="1:13">
+    <row r="24" ht="18" spans="1:13">
       <c r="A24" s="46" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="B24" s="103" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C24" s="104" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D24" s="104"/>
       <c r="E24" s="104"/>
       <c r="F24" s="104"/>
       <c r="G24" s="104"/>
       <c r="H24" s="105" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="I24" s="106" t="s">
         <v>2</v>
@@ -2937,23 +2970,23 @@
       <c r="K24" s="61"/>
       <c r="L24" s="62"/>
     </row>
-    <row r="25" ht="71.25" customHeight="1" spans="1:13">
+    <row r="25" ht="33.75" spans="1:13">
       <c r="A25" s="108"/>
       <c r="B25" s="109" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C25" s="110" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D25" s="111"/>
       <c r="E25" s="111"/>
       <c r="F25" s="111"/>
       <c r="G25" s="109"/>
       <c r="H25" s="111" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="I25" s="112" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="J25" s="113"/>
       <c r="K25" s="114"/>
@@ -2961,7 +2994,7 @@
     </row>
     <row r="26" ht="36.75" customHeight="1" spans="1:13">
       <c r="A26" s="116" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B26" s="117"/>
       <c r="C26" s="117"/>
@@ -2997,7 +3030,7 @@
     </row>
     <row r="37" ht="15" spans="4:10">
       <c r="D37" s="1" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="H37" s="120"/>
       <c r="I37" s="120"/>

--- a/apps/web/server/modules/inquiry/excelTemplate/inquiry.xlsx
+++ b/apps/web/server/modules/inquiry/excelTemplate/inquiry.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12255"/>
+    <workbookView windowWidth="13545" windowHeight="12255"/>
   </bookViews>
   <sheets>
     <sheet name="KK" sheetId="34" r:id="rId1"/>
@@ -27,9 +27,9 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="95" uniqueCount="85">
-  <si>
-    <t>EXPORTER:</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="79" uniqueCount="76">
+  <si>
+    <t>SUPPLIER:</t>
   </si>
   <si>
     <t>Name:</t>
@@ -41,123 +41,93 @@
     <t>QUOTATION SHEET</t>
   </si>
   <si>
+    <t xml:space="preserve">OFFICE ： </t>
+  </si>
+  <si>
+    <t xml:space="preserve">#31 HOUJIE AVENUE, HOUJIE TOWN, DONGGUAN. GUANGDONG CHINA PRC </t>
+  </si>
+  <si>
+    <t>DATE:</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> {{date}}</t>
+  </si>
+  <si>
+    <t>FTY ADDR:</t>
+  </si>
+  <si>
+    <t>{{exporterAddr}}</t>
+  </si>
+  <si>
+    <t>REFER NO.:</t>
+  </si>
+  <si>
+    <t>{{timeNo}}</t>
+  </si>
+  <si>
+    <t>web</t>
+  </si>
+  <si>
+    <t>{{exporterWeb}}</t>
+  </si>
+  <si>
+    <t>email</t>
+  </si>
+  <si>
+    <t>{{exporterEmail}}</t>
+  </si>
+  <si>
+    <t>cc: email:</t>
+  </si>
+  <si>
+    <t>{{exporterPhone}}</t>
+  </si>
+  <si>
+    <t>CLIENT CODE:</t>
+  </si>
+  <si>
+    <t>CLIENT INFO</t>
+  </si>
+  <si>
+    <t>COMPANY NAME:</t>
+  </si>
+  <si>
+    <t>{{clientCompanyName}}</t>
+  </si>
+  <si>
+    <t>PHOTO FOR REFER</t>
+  </si>
+  <si>
+    <t>FULL NAME:</t>
+  </si>
+  <si>
+    <t>{{clientFullName}}</t>
+  </si>
+  <si>
+    <t>EMAIL:</t>
+  </si>
+  <si>
+    <t>{{clientEmail}}</t>
+  </si>
+  <si>
+    <t>{{photoForRefer}}</t>
+  </si>
+  <si>
+    <t>WHATSAPP:</t>
+  </si>
+  <si>
+    <t>{{clientWhatsApp}}</t>
+  </si>
+  <si>
+    <t>TELEGRAM</t>
+  </si>
+  <si>
+    <t>{{clientPhone}}</t>
+  </si>
+  <si>
     <t xml:space="preserve">ADDR： </t>
   </si>
   <si>
-    <t>{{exporterAddr}}</t>
-  </si>
-  <si>
-    <t>web</t>
-  </si>
-  <si>
-    <t>{{exporterWeb}}</t>
-  </si>
-  <si>
-    <t>email</t>
-  </si>
-  <si>
-    <t>{{exporterEmail}}</t>
-  </si>
-  <si>
-    <t>phone</t>
-  </si>
-  <si>
-    <t>{{exporterPhone}}</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FACTORY: </t>
-  </si>
-  <si>
-    <t>Name</t>
-  </si>
-  <si>
-    <t>{{factoryName}}</t>
-  </si>
-  <si>
-    <t>DATE:</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> {{date}}</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ADDR 1: </t>
-  </si>
-  <si>
-    <t>{{factoryAddr1}}</t>
-  </si>
-  <si>
-    <t>{{factoryWeb1}}</t>
-  </si>
-  <si>
-    <t>REFER NO.:</t>
-  </si>
-  <si>
-    <t>{{timeNo}}</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ADDR 2: </t>
-  </si>
-  <si>
-    <t>{{factoryAddr2}}</t>
-  </si>
-  <si>
-    <t>{{factoryWeb2}}</t>
-  </si>
-  <si>
-    <t>CLIENT CODE:</t>
-  </si>
-  <si>
-    <t>ADDR 3：</t>
-  </si>
-  <si>
-    <t>{{factoryAddr3}}</t>
-  </si>
-  <si>
-    <t>{{factoryWeb3}}</t>
-  </si>
-  <si>
-    <t>PI #:</t>
-  </si>
-  <si>
-    <t>CLIENT INFO</t>
-  </si>
-  <si>
-    <t>COMPANY NAME:</t>
-  </si>
-  <si>
-    <t>{{clientCompanyName}}</t>
-  </si>
-  <si>
-    <t>PHOTO FOR REFER</t>
-  </si>
-  <si>
-    <t>FULL NAME:</t>
-  </si>
-  <si>
-    <t>{{clientFullName}}</t>
-  </si>
-  <si>
-    <t>EMAIL:</t>
-  </si>
-  <si>
-    <t>{{clientEmail}}</t>
-  </si>
-  <si>
-    <t>{{photoForRefer}}</t>
-  </si>
-  <si>
-    <t>WHATSAPP:</t>
-  </si>
-  <si>
-    <t>{{clientWhatsApp}}</t>
-  </si>
-  <si>
-    <t>TELEGRAM</t>
-  </si>
-  <si>
-    <t>{{clientPhone}}</t>
-  </si>
-  <si>
     <t>{{clientAddr}}</t>
   </si>
   <si>
@@ -183,6 +153,11 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="微软雅黑"/>
+        <charset val="134"/>
+      </rPr>
       <t>{{</t>
     </r>
     <r>
@@ -287,7 +262,10 @@
     <t>BUYER</t>
   </si>
   <si>
-    <t>SELLER</t>
+    <t xml:space="preserve">{{clientFullName}} </t>
+  </si>
+  <si>
+    <t>SUPPLIER</t>
   </si>
   <si>
     <t>ON BEHALF OF</t>
@@ -296,7 +274,7 @@
     <t>{{exporterBehalf}}</t>
   </si>
   <si>
-    <t>This quotation becomes effective upon mutual signature. Prices and lead times are subject to the final written confirmation.</t>
+    <t>This quotation will be effective upon the mutual signature. The price and other terms are subject to the final written confirmation.</t>
   </si>
   <si>
     <t xml:space="preserve"> </t>
@@ -314,7 +292,7 @@
     <numFmt numFmtId="176" formatCode="[$-409]dd/mmm/yy;@"/>
     <numFmt numFmtId="177" formatCode="0.000_);[Red]\(0.000\)"/>
   </numFmts>
-  <fonts count="42">
+  <fonts count="39">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -368,9 +346,9 @@
     </font>
     <font>
       <b/>
-      <sz val="10"/>
+      <sz val="12"/>
       <color rgb="FF333333"/>
-      <name val="Microsoft YaHei"/>
+      <name val="微软雅黑"/>
       <charset val="134"/>
     </font>
     <font>
@@ -388,31 +366,11 @@
     </font>
     <font>
       <sz val="12"/>
-      <color rgb="FF333333"/>
       <name val="微软雅黑"/>
       <charset val="134"/>
     </font>
     <font>
       <b/>
-      <sz val="12"/>
-      <color rgb="FF333333"/>
-      <name val="微软雅黑"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="12"/>
-      <name val="微软雅黑"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="12"/>
-      <color indexed="12"/>
-      <name val="微软雅黑"/>
-      <charset val="134"/>
-    </font>
-    <font>
       <sz val="12"/>
       <name val="微软雅黑"/>
       <charset val="134"/>
@@ -798,7 +756,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="63">
+  <borders count="61">
     <border>
       <left/>
       <right/>
@@ -864,12 +822,56 @@
       <left style="thick">
         <color auto="1"/>
       </left>
+      <right/>
+      <top style="thick">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thick">
+        <color auto="1"/>
+      </left>
+      <right style="thick">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thick">
+        <color auto="1"/>
+      </left>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thick">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
       <right style="thin">
         <color auto="1"/>
       </right>
-      <top style="thick">
-        <color auto="1"/>
-      </top>
+      <top/>
       <bottom style="thin">
         <color auto="1"/>
       </bottom>
@@ -882,9 +884,7 @@
       <right style="thick">
         <color auto="1"/>
       </right>
-      <top style="thick">
-        <color auto="1"/>
-      </top>
+      <top/>
       <bottom style="thin">
         <color auto="1"/>
       </bottom>
@@ -916,6 +916,97 @@
         <color auto="1"/>
       </top>
       <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thick">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thick">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thick">
+        <color auto="1"/>
+      </left>
+      <right style="thick">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thick">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thick">
+        <color auto="1"/>
+      </left>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thick">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color auto="1"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thick">
         <color auto="1"/>
       </bottom>
       <diagonal/>
@@ -926,6 +1017,86 @@
       <top style="thin">
         <color auto="1"/>
       </top>
+      <bottom style="thick">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thick">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thick">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thick">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thick">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thick">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thick">
+        <color auto="1"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thick">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
       <bottom style="thin">
         <color auto="1"/>
       </bottom>
@@ -937,7 +1108,9 @@
       <top style="thin">
         <color auto="1"/>
       </top>
-      <bottom/>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -948,291 +1121,6 @@
       <top style="thin">
         <color auto="1"/>
       </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thick">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thick">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thick">
-        <color auto="1"/>
-      </left>
-      <right style="thick">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thick">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thick">
-        <color auto="1"/>
-      </left>
-      <right style="medium">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thick">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color auto="1"/>
-      </left>
-      <right/>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thick">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thick">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right/>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thick">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thick">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thick">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thick">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thick">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thick">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thick">
-        <color auto="1"/>
-      </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top/>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thick">
-        <color auto="1"/>
-      </right>
-      <top/>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="medium">
-        <color auto="1"/>
-      </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thick">
-        <color auto="1"/>
-      </left>
-      <right style="medium">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="thick">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thick">
-        <color auto="1"/>
-      </right>
-      <top/>
-      <bottom style="thick">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thick">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top/>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thick">
-        <color auto="1"/>
-      </left>
-      <right/>
-      <top/>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thick">
-        <color auto="1"/>
-      </right>
-      <top/>
       <bottom style="thin">
         <color auto="1"/>
       </bottom>
@@ -1270,54 +1158,69 @@
       <diagonal/>
     </border>
     <border>
+      <left style="thick">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thick">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left/>
       <right style="thick">
         <color auto="1"/>
       </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thick">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right/>
+      <top style="thick">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thick">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
       <top/>
       <bottom/>
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right style="thick">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thick">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right/>
-      <top style="thick">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thick">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="thin">
         <color auto="1"/>
       </left>
@@ -1347,6 +1250,17 @@
       <left style="thin">
         <color auto="1"/>
       </left>
+      <right style="thick">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
       <right/>
       <top/>
       <bottom style="thin">
@@ -1393,6 +1307,36 @@
         <color auto="1"/>
       </top>
       <bottom style="thick">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thick">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thick">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thick">
+        <color auto="1"/>
+      </right>
+      <top style="thick">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
         <color auto="1"/>
       </bottom>
       <diagonal/>
@@ -1594,137 +1538,137 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="53" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="55" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="54" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="54" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="55" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="26" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="56" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="56" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="57" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="6" borderId="58" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="7" borderId="59" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="7" borderId="58" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="8" borderId="60" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="34" fillId="0" borderId="61" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="35" fillId="0" borderId="62" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="37" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="38" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="40" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="40" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="40" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="40" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="40" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="40" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="40" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="40" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="40" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="40" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="40" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="40" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="6" borderId="56" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="7" borderId="57" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="7" borderId="56" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="8" borderId="58" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="59" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="60" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="122">
+  <cellXfs count="105">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -1742,347 +1686,296 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="176" fontId="8" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="177" fontId="8" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="176" fontId="12" fillId="0" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="31" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="177" fontId="12" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="177" fontId="14" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="48" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="50" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="51" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="37" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="46" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="48" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="50" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="51" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="52" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="53" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="54" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="52" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -2433,7 +2326,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:M37"/>
+  <dimension ref="A1:M34"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="19.5" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="15" style="1" customWidth="1"/>
@@ -2484,153 +2377,145 @@
         <v>5</v>
       </c>
       <c r="D2" s="10"/>
-      <c r="E2" s="11"/>
+      <c r="E2" s="10"/>
       <c r="F2" s="10"/>
       <c r="G2" s="10"/>
-      <c r="H2" s="11"/>
+      <c r="H2" s="10"/>
       <c r="I2" s="10"/>
-      <c r="J2" s="12"/>
-      <c r="K2" s="13"/>
-      <c r="L2" s="14"/>
+      <c r="J2" s="11"/>
+      <c r="K2" s="12" t="s">
+        <v>6</v>
+      </c>
+      <c r="L2" s="13" t="s">
+        <v>7</v>
+      </c>
     </row>
     <row r="3" ht="22.5" customHeight="1" spans="1:13">
-      <c r="A3" s="15"/>
-      <c r="B3" s="16" t="s">
-        <v>6</v>
-      </c>
-      <c r="C3" s="17" t="s">
-        <v>7</v>
-      </c>
-      <c r="D3" s="18"/>
-      <c r="E3" s="19" t="s">
+      <c r="A3" s="14"/>
+      <c r="B3" s="15" t="s">
         <v>8</v>
       </c>
-      <c r="F3" s="20" t="s">
+      <c r="C3" s="16" t="s">
         <v>9</v>
       </c>
-      <c r="G3" s="18"/>
-      <c r="H3" s="21"/>
-      <c r="I3" s="18" t="s">
+      <c r="D3" s="16"/>
+      <c r="E3" s="17"/>
+      <c r="F3" s="16"/>
+      <c r="G3" s="16"/>
+      <c r="H3" s="17"/>
+      <c r="I3" s="16"/>
+      <c r="J3" s="18"/>
+      <c r="K3" s="19" t="s">
         <v>10</v>
       </c>
-      <c r="J3" s="22" t="s">
+      <c r="L3" s="20" t="s">
         <v>11</v>
       </c>
-      <c r="K3" s="23"/>
-      <c r="L3" s="24"/>
     </row>
-    <row r="4" ht="18.75" spans="1:13">
-      <c r="A4" s="25" t="s">
+    <row r="4" ht="22.5" customHeight="1" spans="1:13">
+      <c r="A4" s="21"/>
+      <c r="B4" s="22" t="s">
         <v>12</v>
       </c>
-      <c r="B4" s="26" t="s">
+      <c r="C4" s="23" t="s">
         <v>13</v>
       </c>
-      <c r="C4" s="27" t="s">
+      <c r="D4" s="24"/>
+      <c r="E4" s="25" t="s">
         <v>14</v>
       </c>
-      <c r="D4" s="27"/>
-      <c r="E4" s="27"/>
-      <c r="F4" s="27"/>
-      <c r="G4" s="27"/>
-      <c r="H4" s="28"/>
-      <c r="I4" s="27" t="s">
-        <v>10</v>
-      </c>
-      <c r="J4" s="29" t="s">
-        <v>11</v>
-      </c>
-      <c r="K4" s="30" t="s">
+      <c r="F4" s="26" t="s">
         <v>15</v>
       </c>
-      <c r="L4" s="31" t="s">
+      <c r="G4" s="24"/>
+      <c r="H4" s="27"/>
+      <c r="I4" s="24" t="s">
         <v>16</v>
       </c>
+      <c r="J4" s="28" t="s">
+        <v>17</v>
+      </c>
+      <c r="K4" s="19" t="s">
+        <v>18</v>
+      </c>
+      <c r="L4" s="20"/>
     </row>
-    <row r="5" ht="18" spans="1:13">
-      <c r="A5" s="32"/>
-      <c r="B5" s="33" t="s">
-        <v>17</v>
-      </c>
-      <c r="C5" s="34" t="s">
-        <v>18</v>
-      </c>
-      <c r="D5" s="34"/>
-      <c r="E5" s="34"/>
-      <c r="F5" s="34"/>
-      <c r="G5" s="34"/>
-      <c r="H5" s="35"/>
-      <c r="I5" s="34" t="s">
-        <v>6</v>
-      </c>
-      <c r="J5" s="36" t="s">
+    <row r="5" ht="18.75" spans="1:13">
+      <c r="A5" s="29" t="s">
         <v>19</v>
       </c>
-      <c r="K5" s="37" t="s">
+      <c r="B5" s="30" t="s">
         <v>20</v>
       </c>
-      <c r="L5" s="38" t="s">
+      <c r="C5" s="31"/>
+      <c r="D5" s="32" t="s">
         <v>21</v>
       </c>
+      <c r="E5" s="33"/>
+      <c r="F5" s="33"/>
+      <c r="G5" s="33"/>
+      <c r="H5" s="33"/>
+      <c r="I5" s="33"/>
+      <c r="J5" s="34"/>
+      <c r="K5" s="35" t="s">
+        <v>22</v>
+      </c>
+      <c r="L5" s="36"/>
     </row>
-    <row r="6" ht="18" spans="1:13">
-      <c r="A6" s="32"/>
-      <c r="B6" s="39" t="s">
-        <v>22</v>
-      </c>
-      <c r="C6" s="10" t="s">
+    <row r="6" ht="17.25" spans="1:13">
+      <c r="A6" s="37"/>
+      <c r="B6" s="38" t="s">
         <v>23</v>
       </c>
-      <c r="D6" s="10"/>
-      <c r="E6" s="10"/>
-      <c r="F6" s="10"/>
-      <c r="G6" s="10"/>
-      <c r="H6" s="40"/>
-      <c r="I6" s="34" t="s">
-        <v>6</v>
-      </c>
-      <c r="J6" s="36" t="s">
+      <c r="C6" s="39"/>
+      <c r="D6" s="40" t="s">
         <v>24</v>
       </c>
-      <c r="K6" s="37" t="s">
+      <c r="E6" s="40"/>
+      <c r="F6" s="40"/>
+      <c r="G6" s="40"/>
+      <c r="H6" s="41" t="s">
         <v>25</v>
       </c>
-      <c r="L6" s="38"/>
+      <c r="I6" s="40" t="s">
+        <v>26</v>
+      </c>
+      <c r="J6" s="42"/>
+      <c r="K6" s="43" t="s">
+        <v>27</v>
+      </c>
+      <c r="L6" s="44"/>
     </row>
-    <row r="7" ht="18.75" spans="1:13">
-      <c r="A7" s="41"/>
-      <c r="B7" s="16" t="s">
-        <v>26</v>
-      </c>
-      <c r="C7" s="17" t="s">
-        <v>27</v>
-      </c>
-      <c r="D7" s="18"/>
-      <c r="E7" s="18"/>
-      <c r="F7" s="18"/>
-      <c r="G7" s="18"/>
-      <c r="H7" s="21"/>
-      <c r="I7" s="42" t="s">
-        <v>6</v>
-      </c>
-      <c r="J7" s="43" t="s">
+    <row r="7" ht="17.25" spans="1:13">
+      <c r="A7" s="37"/>
+      <c r="B7" s="38" t="s">
         <v>28</v>
       </c>
-      <c r="K7" s="44" t="s">
+      <c r="C7" s="39"/>
+      <c r="D7" s="40" t="s">
         <v>29</v>
       </c>
-      <c r="L7" s="45"/>
+      <c r="E7" s="40"/>
+      <c r="F7" s="40"/>
+      <c r="G7" s="40"/>
+      <c r="H7" s="41" t="s">
+        <v>30</v>
+      </c>
+      <c r="I7" s="40" t="s">
+        <v>31</v>
+      </c>
+      <c r="J7" s="42"/>
+      <c r="K7" s="45"/>
+      <c r="L7" s="46"/>
     </row>
-    <row r="8" ht="18.75" spans="1:13">
-      <c r="A8" s="46" t="s">
-        <v>30</v>
-      </c>
-      <c r="B8" s="47" t="s">
-        <v>31</v>
-      </c>
-      <c r="C8" s="48"/>
-      <c r="D8" s="49" t="s">
+    <row r="8" ht="18" spans="1:13">
+      <c r="A8" s="47"/>
+      <c r="B8" s="48" t="s">
         <v>32</v>
+      </c>
+      <c r="C8" s="49"/>
+      <c r="D8" s="50" t="s">
+        <v>33</v>
       </c>
       <c r="E8" s="50"/>
       <c r="F8" s="50"/>
@@ -2638,428 +2523,366 @@
       <c r="H8" s="50"/>
       <c r="I8" s="50"/>
       <c r="J8" s="51"/>
-      <c r="K8" s="52" t="s">
-        <v>33</v>
-      </c>
-      <c r="L8" s="53"/>
+      <c r="K8" s="45"/>
+      <c r="L8" s="46"/>
+      <c r="M8" s="52"/>
     </row>
-    <row r="9" ht="17.25" spans="1:13">
-      <c r="A9" s="54"/>
-      <c r="B9" s="55" t="s">
+    <row r="9" ht="18" spans="1:13">
+      <c r="A9" s="29" t="s">
         <v>34</v>
       </c>
-      <c r="C9" s="56"/>
-      <c r="D9" s="57" t="s">
+      <c r="B9" s="53" t="s">
         <v>35</v>
       </c>
-      <c r="E9" s="57"/>
-      <c r="F9" s="57"/>
-      <c r="G9" s="57"/>
-      <c r="H9" s="10" t="s">
+      <c r="C9" s="54" t="s">
         <v>36</v>
       </c>
-      <c r="I9" s="57" t="s">
+      <c r="D9" s="55"/>
+      <c r="E9" s="55"/>
+      <c r="F9" s="56"/>
+      <c r="G9" s="57" t="s">
         <v>37</v>
       </c>
-      <c r="J9" s="58"/>
-      <c r="K9" s="59" t="s">
+      <c r="H9" s="58" t="s">
         <v>38</v>
       </c>
-      <c r="L9" s="60"/>
+      <c r="I9" s="59" t="s">
+        <v>39</v>
+      </c>
+      <c r="J9" s="60" t="s">
+        <v>40</v>
+      </c>
+      <c r="K9" s="45"/>
+      <c r="L9" s="46"/>
     </row>
-    <row r="10" ht="17.25" spans="1:13">
-      <c r="A10" s="54"/>
-      <c r="B10" s="55" t="s">
-        <v>39</v>
-      </c>
-      <c r="C10" s="56"/>
-      <c r="D10" s="57" t="s">
-        <v>40</v>
-      </c>
-      <c r="E10" s="57"/>
-      <c r="F10" s="57"/>
-      <c r="G10" s="57"/>
-      <c r="H10" s="10" t="s">
+    <row r="10" ht="51.75" spans="1:13">
+      <c r="A10" s="37"/>
+      <c r="B10" s="61" t="s">
         <v>41</v>
       </c>
-      <c r="I10" s="57" t="s">
+      <c r="C10" s="62" t="s">
         <v>42</v>
       </c>
-      <c r="J10" s="58"/>
-      <c r="K10" s="61"/>
-      <c r="L10" s="62"/>
+      <c r="D10" s="63"/>
+      <c r="E10" s="63"/>
+      <c r="F10" s="64"/>
+      <c r="G10" s="65" t="s">
+        <v>43</v>
+      </c>
+      <c r="H10" s="66"/>
+      <c r="I10" s="65" t="s">
+        <v>44</v>
+      </c>
+      <c r="J10" s="67" t="s">
+        <v>45</v>
+      </c>
+      <c r="K10" s="45"/>
+      <c r="L10" s="46"/>
     </row>
-    <row r="11" ht="18" spans="1:13">
-      <c r="A11" s="63"/>
-      <c r="B11" s="64" t="s">
-        <v>4</v>
-      </c>
-      <c r="C11" s="65"/>
-      <c r="D11" s="66" t="s">
-        <v>43</v>
-      </c>
-      <c r="E11" s="66"/>
-      <c r="F11" s="66"/>
-      <c r="G11" s="66"/>
-      <c r="H11" s="66"/>
-      <c r="I11" s="66"/>
-      <c r="J11" s="67"/>
-      <c r="K11" s="61"/>
-      <c r="L11" s="62"/>
-      <c r="M11" s="68"/>
+    <row r="11" ht="22.5" customHeight="1" spans="1:13">
+      <c r="A11" s="47"/>
+      <c r="B11" s="68"/>
+      <c r="C11" s="68"/>
+      <c r="D11" s="68"/>
+      <c r="E11" s="68"/>
+      <c r="F11" s="68"/>
+      <c r="G11" s="69" t="s">
+        <v>46</v>
+      </c>
+      <c r="H11" s="69"/>
+      <c r="I11" s="70" t="s">
+        <v>47</v>
+      </c>
+      <c r="J11" s="71"/>
+      <c r="K11" s="45"/>
+      <c r="L11" s="46"/>
     </row>
-    <row r="12" ht="18" spans="1:13">
-      <c r="A12" s="46" t="s">
-        <v>44</v>
-      </c>
-      <c r="B12" s="69" t="s">
-        <v>45</v>
-      </c>
-      <c r="C12" s="70" t="s">
-        <v>46</v>
-      </c>
-      <c r="D12" s="71"/>
-      <c r="E12" s="71"/>
-      <c r="F12" s="72"/>
-      <c r="G12" s="73" t="s">
-        <v>47</v>
-      </c>
-      <c r="H12" s="74" t="s">
+    <row r="12" ht="39.75" customHeight="1" spans="1:13">
+      <c r="A12" s="29" t="s">
         <v>48</v>
       </c>
-      <c r="I12" s="75" t="s">
+      <c r="B12" s="72" t="s">
         <v>49</v>
       </c>
-      <c r="J12" s="76" t="s">
+      <c r="C12" s="73"/>
+      <c r="D12" s="74" t="s">
         <v>50</v>
       </c>
-      <c r="K12" s="61"/>
-      <c r="L12" s="62"/>
+      <c r="E12" s="74"/>
+      <c r="F12" s="74"/>
+      <c r="G12" s="74"/>
+      <c r="H12" s="74"/>
+      <c r="I12" s="74"/>
+      <c r="J12" s="75"/>
+      <c r="K12" s="45"/>
+      <c r="L12" s="46"/>
     </row>
-    <row r="13" ht="51.75" spans="1:13">
-      <c r="A13" s="54"/>
-      <c r="B13" s="77" t="s">
+    <row r="13" ht="22.5" customHeight="1" spans="1:13">
+      <c r="A13" s="37"/>
+      <c r="B13" s="76" t="s">
         <v>51</v>
       </c>
-      <c r="C13" s="78" t="s">
+      <c r="C13" s="77"/>
+      <c r="D13" s="78" t="s">
         <v>52</v>
       </c>
-      <c r="D13" s="79"/>
-      <c r="E13" s="79"/>
-      <c r="F13" s="80"/>
-      <c r="G13" s="81" t="s">
-        <v>53</v>
-      </c>
-      <c r="H13" s="82"/>
-      <c r="I13" s="81" t="s">
-        <v>54</v>
-      </c>
-      <c r="J13" s="83" t="s">
-        <v>55</v>
-      </c>
-      <c r="K13" s="61"/>
-      <c r="L13" s="62"/>
+      <c r="E13" s="78"/>
+      <c r="F13" s="78"/>
+      <c r="G13" s="78"/>
+      <c r="H13" s="78"/>
+      <c r="I13" s="78"/>
+      <c r="J13" s="79"/>
+      <c r="K13" s="45"/>
+      <c r="L13" s="46"/>
     </row>
     <row r="14" ht="22.5" customHeight="1" spans="1:13">
-      <c r="A14" s="63"/>
-      <c r="B14" s="84"/>
-      <c r="C14" s="84"/>
-      <c r="D14" s="84"/>
-      <c r="E14" s="84"/>
-      <c r="F14" s="84"/>
-      <c r="G14" s="85" t="s">
+      <c r="A14" s="37"/>
+      <c r="B14" s="76" t="s">
+        <v>53</v>
+      </c>
+      <c r="C14" s="77"/>
+      <c r="D14" s="78" t="s">
+        <v>54</v>
+      </c>
+      <c r="E14" s="78"/>
+      <c r="F14" s="78"/>
+      <c r="G14" s="78"/>
+      <c r="H14" s="78"/>
+      <c r="I14" s="78"/>
+      <c r="J14" s="79"/>
+      <c r="K14" s="45"/>
+      <c r="L14" s="46"/>
+      <c r="M14" s="80"/>
+    </row>
+    <row r="15" ht="26" customHeight="1" spans="1:13">
+      <c r="A15" s="37"/>
+      <c r="B15" s="76" t="s">
+        <v>55</v>
+      </c>
+      <c r="C15" s="77"/>
+      <c r="D15" s="78" t="s">
         <v>56</v>
       </c>
-      <c r="H14" s="85"/>
-      <c r="I14" s="86" t="s">
+      <c r="E15" s="78"/>
+      <c r="F15" s="78"/>
+      <c r="G15" s="78"/>
+      <c r="H15" s="78"/>
+      <c r="I15" s="78"/>
+      <c r="J15" s="79"/>
+      <c r="K15" s="45"/>
+      <c r="L15" s="46"/>
+    </row>
+    <row r="16" ht="34.5" customHeight="1" spans="1:13">
+      <c r="A16" s="47"/>
+      <c r="B16" s="81" t="s">
         <v>57</v>
       </c>
-      <c r="J14" s="87"/>
-      <c r="K14" s="61"/>
-      <c r="L14" s="62"/>
-    </row>
-    <row r="15" ht="39.75" customHeight="1" spans="1:13">
-      <c r="A15" s="46" t="s">
+      <c r="C16" s="82"/>
+      <c r="D16" s="83" t="s">
         <v>58</v>
       </c>
-      <c r="B15" s="88" t="s">
-        <v>59</v>
-      </c>
-      <c r="C15" s="89"/>
-      <c r="D15" s="90" t="s">
-        <v>60</v>
-      </c>
-      <c r="E15" s="90"/>
-      <c r="F15" s="90"/>
-      <c r="G15" s="90"/>
-      <c r="H15" s="90"/>
-      <c r="I15" s="90"/>
-      <c r="J15" s="91"/>
-      <c r="K15" s="61"/>
-      <c r="L15" s="62"/>
-    </row>
-    <row r="16" ht="22.5" customHeight="1" spans="1:13">
-      <c r="A16" s="54"/>
-      <c r="B16" s="92" t="s">
-        <v>61</v>
-      </c>
-      <c r="C16" s="93"/>
-      <c r="D16" s="94" t="s">
-        <v>62</v>
-      </c>
-      <c r="E16" s="94"/>
-      <c r="F16" s="94"/>
-      <c r="G16" s="94"/>
-      <c r="H16" s="94"/>
-      <c r="I16" s="94"/>
-      <c r="J16" s="95"/>
-      <c r="K16" s="61"/>
-      <c r="L16" s="62"/>
+      <c r="E16" s="83"/>
+      <c r="F16" s="83"/>
+      <c r="G16" s="83"/>
+      <c r="H16" s="83"/>
+      <c r="I16" s="83"/>
+      <c r="J16" s="84"/>
+      <c r="K16" s="45"/>
+      <c r="L16" s="46"/>
+      <c r="M16" s="80"/>
     </row>
     <row r="17" ht="22.5" customHeight="1" spans="1:13">
-      <c r="A17" s="54"/>
-      <c r="B17" s="92" t="s">
+      <c r="A17" s="29" t="s">
+        <v>59</v>
+      </c>
+      <c r="B17" s="72" t="s">
+        <v>60</v>
+      </c>
+      <c r="C17" s="73"/>
+      <c r="D17" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="E17" s="16"/>
+      <c r="F17" s="16"/>
+      <c r="G17" s="16"/>
+      <c r="H17" s="16"/>
+      <c r="I17" s="16"/>
+      <c r="J17" s="18"/>
+      <c r="K17" s="45"/>
+      <c r="L17" s="46"/>
+    </row>
+    <row r="18" ht="22.5" customHeight="1" spans="1:13">
+      <c r="A18" s="37"/>
+      <c r="B18" s="76" t="s">
+        <v>62</v>
+      </c>
+      <c r="C18" s="77"/>
+      <c r="D18" s="78" t="s">
         <v>63</v>
       </c>
-      <c r="C17" s="93"/>
-      <c r="D17" s="94" t="s">
+      <c r="E18" s="78"/>
+      <c r="F18" s="78"/>
+      <c r="G18" s="78"/>
+      <c r="H18" s="78"/>
+      <c r="I18" s="78"/>
+      <c r="J18" s="79"/>
+      <c r="K18" s="45"/>
+      <c r="L18" s="46"/>
+    </row>
+    <row r="19" ht="22.5" customHeight="1" spans="1:13">
+      <c r="A19" s="37"/>
+      <c r="B19" s="76" t="s">
         <v>64</v>
       </c>
-      <c r="E17" s="94"/>
-      <c r="F17" s="94"/>
-      <c r="G17" s="94"/>
-      <c r="H17" s="94"/>
-      <c r="I17" s="94"/>
-      <c r="J17" s="95"/>
-      <c r="K17" s="61"/>
-      <c r="L17" s="62"/>
-      <c r="M17" s="96"/>
-    </row>
-    <row r="18" ht="26" customHeight="1" spans="1:13">
-      <c r="A18" s="54"/>
-      <c r="B18" s="92" t="s">
+      <c r="C19" s="77"/>
+      <c r="D19" s="78" t="s">
         <v>65</v>
       </c>
-      <c r="C18" s="93"/>
-      <c r="D18" s="94" t="s">
-        <v>66</v>
-      </c>
-      <c r="E18" s="94"/>
-      <c r="F18" s="94"/>
-      <c r="G18" s="94"/>
-      <c r="H18" s="94"/>
-      <c r="I18" s="94"/>
-      <c r="J18" s="95"/>
-      <c r="K18" s="61"/>
-      <c r="L18" s="62"/>
-    </row>
-    <row r="19" ht="34.5" customHeight="1" spans="1:13">
-      <c r="A19" s="63"/>
-      <c r="B19" s="97" t="s">
-        <v>67</v>
-      </c>
-      <c r="C19" s="98"/>
-      <c r="D19" s="99" t="s">
-        <v>68</v>
-      </c>
-      <c r="E19" s="99"/>
-      <c r="F19" s="99"/>
-      <c r="G19" s="99"/>
-      <c r="H19" s="99"/>
-      <c r="I19" s="99"/>
-      <c r="J19" s="100"/>
-      <c r="K19" s="61"/>
-      <c r="L19" s="62"/>
-      <c r="M19" s="96"/>
+      <c r="E19" s="78"/>
+      <c r="F19" s="78"/>
+      <c r="G19" s="78"/>
+      <c r="H19" s="78"/>
+      <c r="I19" s="78"/>
+      <c r="J19" s="79"/>
+      <c r="K19" s="45"/>
+      <c r="L19" s="46"/>
     </row>
     <row r="20" ht="22.5" customHeight="1" spans="1:13">
-      <c r="A20" s="46" t="s">
+      <c r="A20" s="47"/>
+      <c r="B20" s="85" t="s">
+        <v>66</v>
+      </c>
+      <c r="C20" s="82"/>
+      <c r="D20" s="83" t="s">
+        <v>67</v>
+      </c>
+      <c r="E20" s="83"/>
+      <c r="F20" s="83"/>
+      <c r="G20" s="83"/>
+      <c r="H20" s="83"/>
+      <c r="I20" s="83"/>
+      <c r="J20" s="84"/>
+      <c r="K20" s="45"/>
+      <c r="L20" s="46"/>
+    </row>
+    <row r="21" ht="18" spans="1:13">
+      <c r="A21" s="29" t="s">
+        <v>68</v>
+      </c>
+      <c r="B21" s="86" t="s">
         <v>69</v>
       </c>
-      <c r="B20" s="88" t="s">
+      <c r="C21" s="87" t="s">
         <v>70</v>
       </c>
-      <c r="C20" s="89"/>
-      <c r="D20" s="34" t="s">
+      <c r="D21" s="87"/>
+      <c r="E21" s="87"/>
+      <c r="F21" s="87"/>
+      <c r="G21" s="87"/>
+      <c r="H21" s="88" t="s">
         <v>71</v>
       </c>
-      <c r="E20" s="34"/>
-      <c r="F20" s="34"/>
-      <c r="G20" s="34"/>
-      <c r="H20" s="34"/>
-      <c r="I20" s="34"/>
-      <c r="J20" s="101"/>
-      <c r="K20" s="61"/>
-      <c r="L20" s="62"/>
+      <c r="I21" s="89" t="s">
+        <v>2</v>
+      </c>
+      <c r="J21" s="90"/>
+      <c r="K21" s="45"/>
+      <c r="L21" s="46"/>
     </row>
-    <row r="21" ht="22.5" customHeight="1" spans="1:13">
-      <c r="A21" s="54"/>
-      <c r="B21" s="92" t="s">
+    <row r="22" ht="33.75" spans="1:13">
+      <c r="A22" s="91"/>
+      <c r="B22" s="92" t="s">
         <v>72</v>
       </c>
-      <c r="C21" s="93"/>
-      <c r="D21" s="94" t="s">
-        <v>73</v>
-      </c>
-      <c r="E21" s="94"/>
-      <c r="F21" s="94"/>
-      <c r="G21" s="94"/>
-      <c r="H21" s="94"/>
-      <c r="I21" s="94"/>
-      <c r="J21" s="95"/>
-      <c r="K21" s="61"/>
-      <c r="L21" s="62"/>
-    </row>
-    <row r="22" ht="22.5" customHeight="1" spans="1:13">
-      <c r="A22" s="54"/>
-      <c r="B22" s="92" t="s">
-        <v>74</v>
-      </c>
-      <c r="C22" s="93"/>
-      <c r="D22" s="94" t="s">
-        <v>75</v>
-      </c>
+      <c r="C22" s="93" t="s">
+        <v>21</v>
+      </c>
+      <c r="D22" s="94"/>
       <c r="E22" s="94"/>
       <c r="F22" s="94"/>
-      <c r="G22" s="94"/>
-      <c r="H22" s="94"/>
-      <c r="I22" s="94"/>
-      <c r="J22" s="95"/>
-      <c r="K22" s="61"/>
-      <c r="L22" s="62"/>
+      <c r="G22" s="92"/>
+      <c r="H22" s="94" t="s">
+        <v>72</v>
+      </c>
+      <c r="I22" s="95" t="s">
+        <v>73</v>
+      </c>
+      <c r="J22" s="96"/>
+      <c r="K22" s="97"/>
+      <c r="L22" s="98"/>
     </row>
-    <row r="23" ht="22.5" customHeight="1" spans="1:13">
-      <c r="A23" s="63"/>
-      <c r="B23" s="102" t="s">
-        <v>76</v>
-      </c>
-      <c r="C23" s="98"/>
-      <c r="D23" s="99" t="s">
-        <v>77</v>
-      </c>
-      <c r="E23" s="99"/>
-      <c r="F23" s="99"/>
-      <c r="G23" s="99"/>
-      <c r="H23" s="99"/>
-      <c r="I23" s="99"/>
+    <row r="23" ht="36.75" customHeight="1" spans="1:13">
+      <c r="A23" s="99" t="s">
+        <v>74</v>
+      </c>
+      <c r="B23" s="100"/>
+      <c r="C23" s="100"/>
+      <c r="D23" s="100"/>
+      <c r="E23" s="100"/>
+      <c r="F23" s="100"/>
+      <c r="G23" s="100"/>
+      <c r="H23" s="100"/>
+      <c r="I23" s="100"/>
       <c r="J23" s="100"/>
-      <c r="K23" s="61"/>
-      <c r="L23" s="62"/>
+      <c r="K23" s="100"/>
+      <c r="L23" s="101"/>
     </row>
-    <row r="24" ht="18" spans="1:13">
-      <c r="A24" s="46" t="s">
-        <v>78</v>
-      </c>
-      <c r="B24" s="103" t="s">
-        <v>79</v>
-      </c>
-      <c r="C24" s="104" t="s">
-        <v>32</v>
-      </c>
-      <c r="D24" s="104"/>
-      <c r="E24" s="104"/>
-      <c r="F24" s="104"/>
-      <c r="G24" s="104"/>
-      <c r="H24" s="105" t="s">
-        <v>80</v>
-      </c>
-      <c r="I24" s="106" t="s">
-        <v>2</v>
-      </c>
-      <c r="J24" s="107"/>
-      <c r="K24" s="61"/>
-      <c r="L24" s="62"/>
+    <row r="24" ht="15.75" spans="1:13">
+      <c r="D24" s="102"/>
+      <c r="H24" s="103"/>
+      <c r="I24" s="103"/>
+      <c r="J24" s="103"/>
+      <c r="M24" s="104"/>
     </row>
-    <row r="25" ht="33.75" spans="1:13">
-      <c r="A25" s="108"/>
-      <c r="B25" s="109" t="s">
-        <v>81</v>
-      </c>
-      <c r="C25" s="110" t="s">
-        <v>35</v>
-      </c>
-      <c r="D25" s="111"/>
-      <c r="E25" s="111"/>
-      <c r="F25" s="111"/>
-      <c r="G25" s="109"/>
-      <c r="H25" s="111" t="s">
-        <v>81</v>
-      </c>
-      <c r="I25" s="112" t="s">
-        <v>82</v>
-      </c>
-      <c r="J25" s="113"/>
-      <c r="K25" s="114"/>
-      <c r="L25" s="115"/>
+    <row r="25" ht="13.5" spans="1:13">
+      <c r="M25" s="104"/>
     </row>
-    <row r="26" ht="36.75" customHeight="1" spans="1:13">
-      <c r="A26" s="116" t="s">
-        <v>83</v>
-      </c>
-      <c r="B26" s="117"/>
-      <c r="C26" s="117"/>
-      <c r="D26" s="117"/>
-      <c r="E26" s="117"/>
-      <c r="F26" s="117"/>
-      <c r="G26" s="117"/>
-      <c r="H26" s="117"/>
-      <c r="I26" s="117"/>
-      <c r="J26" s="117"/>
-      <c r="K26" s="117"/>
-      <c r="L26" s="118"/>
+    <row r="32" ht="14.25" spans="1:13">
+      <c r="H32" s="103"/>
+      <c r="I32" s="103"/>
+      <c r="J32" s="103"/>
     </row>
-    <row r="27" ht="15.75" spans="1:13">
-      <c r="D27" s="119"/>
-      <c r="H27" s="120"/>
-      <c r="I27" s="120"/>
-      <c r="J27" s="120"/>
-      <c r="M27" s="121"/>
+    <row r="33" ht="14.25" spans="4:10">
+      <c r="H33" s="103"/>
+      <c r="I33" s="103"/>
+      <c r="J33" s="103"/>
     </row>
-    <row r="28" ht="13.5" spans="1:13">
-      <c r="M28" s="121"/>
-    </row>
-    <row r="35" ht="14.25" spans="4:10">
-      <c r="H35" s="120"/>
-      <c r="I35" s="120"/>
-      <c r="J35" s="120"/>
-    </row>
-    <row r="36" ht="14.25" spans="4:10">
-      <c r="H36" s="120"/>
-      <c r="I36" s="120"/>
-      <c r="J36" s="120"/>
-    </row>
-    <row r="37" ht="15" spans="4:10">
-      <c r="D37" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="H37" s="120"/>
-      <c r="I37" s="120"/>
-      <c r="J37" s="120"/>
+    <row r="34" ht="15" spans="4:10">
+      <c r="D34" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="H34" s="103"/>
+      <c r="I34" s="103"/>
+      <c r="J34" s="103"/>
     </row>
   </sheetData>
-  <mergeCells count="54">
+  <mergeCells count="50">
     <mergeCell ref="C1:J1"/>
+    <mergeCell ref="K1:L1"/>
     <mergeCell ref="C2:J2"/>
-    <mergeCell ref="C3:D3"/>
-    <mergeCell ref="F3:H3"/>
-    <mergeCell ref="C4:H4"/>
-    <mergeCell ref="C5:H5"/>
-    <mergeCell ref="C6:H6"/>
-    <mergeCell ref="C7:H7"/>
+    <mergeCell ref="C3:J3"/>
+    <mergeCell ref="C4:D4"/>
+    <mergeCell ref="F4:H4"/>
+    <mergeCell ref="B5:C5"/>
+    <mergeCell ref="D5:J5"/>
+    <mergeCell ref="K5:L5"/>
+    <mergeCell ref="B6:C6"/>
+    <mergeCell ref="D6:G6"/>
+    <mergeCell ref="I6:J6"/>
+    <mergeCell ref="B7:C7"/>
+    <mergeCell ref="D7:G7"/>
+    <mergeCell ref="I7:J7"/>
     <mergeCell ref="B8:C8"/>
     <mergeCell ref="D8:J8"/>
-    <mergeCell ref="K8:L8"/>
-    <mergeCell ref="B9:C9"/>
-    <mergeCell ref="D9:G9"/>
-    <mergeCell ref="I9:J9"/>
-    <mergeCell ref="B10:C10"/>
-    <mergeCell ref="D10:G10"/>
-    <mergeCell ref="I10:J10"/>
-    <mergeCell ref="B11:C11"/>
-    <mergeCell ref="D11:J11"/>
-    <mergeCell ref="C12:F12"/>
-    <mergeCell ref="C13:F13"/>
-    <mergeCell ref="B14:F14"/>
+    <mergeCell ref="C9:F9"/>
+    <mergeCell ref="C10:F10"/>
+    <mergeCell ref="B11:F11"/>
+    <mergeCell ref="B12:C12"/>
+    <mergeCell ref="D12:J12"/>
+    <mergeCell ref="B13:C13"/>
+    <mergeCell ref="D13:J13"/>
+    <mergeCell ref="B14:C14"/>
+    <mergeCell ref="D14:J14"/>
     <mergeCell ref="B15:C15"/>
     <mergeCell ref="D15:J15"/>
     <mergeCell ref="B16:C16"/>
@@ -3072,30 +2895,22 @@
     <mergeCell ref="D19:J19"/>
     <mergeCell ref="B20:C20"/>
     <mergeCell ref="D20:J20"/>
-    <mergeCell ref="B21:C21"/>
-    <mergeCell ref="D21:J21"/>
-    <mergeCell ref="B22:C22"/>
-    <mergeCell ref="D22:J22"/>
-    <mergeCell ref="B23:C23"/>
-    <mergeCell ref="D23:J23"/>
-    <mergeCell ref="C24:G24"/>
-    <mergeCell ref="I24:J24"/>
-    <mergeCell ref="C25:G25"/>
-    <mergeCell ref="I25:J25"/>
-    <mergeCell ref="A26:L26"/>
-    <mergeCell ref="A1:A3"/>
-    <mergeCell ref="A4:A7"/>
-    <mergeCell ref="A8:A11"/>
-    <mergeCell ref="A12:A14"/>
-    <mergeCell ref="A15:A19"/>
-    <mergeCell ref="A20:A23"/>
-    <mergeCell ref="A24:A25"/>
-    <mergeCell ref="K9:L25"/>
-    <mergeCell ref="K1:L3"/>
+    <mergeCell ref="C21:G21"/>
+    <mergeCell ref="I21:J21"/>
+    <mergeCell ref="C22:G22"/>
+    <mergeCell ref="I22:J22"/>
+    <mergeCell ref="A23:L23"/>
+    <mergeCell ref="A1:A4"/>
+    <mergeCell ref="A5:A8"/>
+    <mergeCell ref="A9:A11"/>
+    <mergeCell ref="A12:A16"/>
+    <mergeCell ref="A17:A20"/>
+    <mergeCell ref="A21:A22"/>
+    <mergeCell ref="K6:L22"/>
   </mergeCells>
   <hyperlinks>
-    <hyperlink ref="F3" r:id="rId1" display="{{exporterEmail}}"/>
-    <hyperlink ref="C3" r:id="rId2" display="{{exporterWeb}}"/>
+    <hyperlink ref="F4" r:id="rId1" display="{{exporterEmail}}"/>
+    <hyperlink ref="C4" r:id="rId2" display="{{exporterWeb}}"/>
   </hyperlinks>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
   <pageMargins left="0" right="0" top="0" bottom="0" header="0.118055555555556" footer="0.118055555555556"/>

--- a/apps/web/server/modules/inquiry/excelTemplate/inquiry.xlsx
+++ b/apps/web/server/modules/inquiry/excelTemplate/inquiry.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="13545" windowHeight="12255"/>
+    <workbookView windowWidth="27945" windowHeight="12255"/>
   </bookViews>
   <sheets>
     <sheet name="KK" sheetId="34" r:id="rId1"/>

--- a/apps/web/server/modules/inquiry/excelTemplate/inquiry.xlsx
+++ b/apps/web/server/modules/inquiry/excelTemplate/inquiry.xlsx
@@ -44,7 +44,7 @@
     <t xml:space="preserve">OFFICE ： </t>
   </si>
   <si>
-    <t xml:space="preserve">#31 HOUJIE AVENUE, HOUJIE TOWN, DONGGUAN. GUANGDONG CHINA PRC </t>
+    <t>{{exporterAddr}}</t>
   </si>
   <si>
     <t>DATE:</t>
@@ -56,7 +56,7 @@
     <t>FTY ADDR:</t>
   </si>
   <si>
-    <t>{{exporterAddr}}</t>
+    <t>{{factoryAddr}}</t>
   </si>
   <si>
     <t>REFER NO.:</t>
@@ -68,19 +68,19 @@
     <t>web</t>
   </si>
   <si>
-    <t>{{exporterWeb}}</t>
+    <t>{{fatoryWeb}}</t>
   </si>
   <si>
     <t>email</t>
   </si>
   <si>
+    <t>{{factoryEmail}}</t>
+  </si>
+  <si>
+    <t>cc: email:</t>
+  </si>
+  <si>
     <t>{{exporterEmail}}</t>
-  </si>
-  <si>
-    <t>cc: email:</t>
-  </si>
-  <si>
-    <t>{{exporterPhone}}</t>
   </si>
   <si>
     <t>CLIENT CODE:</t>
@@ -2909,8 +2909,8 @@
     <mergeCell ref="K6:L22"/>
   </mergeCells>
   <hyperlinks>
-    <hyperlink ref="F4" r:id="rId1" display="{{exporterEmail}}"/>
-    <hyperlink ref="C4" r:id="rId2" display="{{exporterWeb}}"/>
+    <hyperlink ref="F4" r:id="rId1" display="{{factoryEmail}}"/>
+    <hyperlink ref="C4" r:id="rId2" display="{{fatoryWeb}}"/>
   </hyperlinks>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
   <pageMargins left="0" right="0" top="0" bottom="0" header="0.118055555555556" footer="0.118055555555556"/>

--- a/apps/web/server/modules/inquiry/excelTemplate/inquiry.xlsx
+++ b/apps/web/server/modules/inquiry/excelTemplate/inquiry.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="79" uniqueCount="76">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="78">
   <si>
     <t>SUPPLIER:</t>
   </si>
@@ -140,10 +140,10 @@
     <t>PRODUCT DESCRIPTION</t>
   </si>
   <si>
-    <t>UNITS</t>
-  </si>
-  <si>
-    <t>(USD/UNIT)</t>
+    <t>PAIRS</t>
+  </si>
+  <si>
+    <t>USD/PAIR</t>
   </si>
   <si>
     <t>(TTL:VALUE)</t>
@@ -190,10 +190,16 @@
     <t>{{termsRemark1}}</t>
   </si>
   <si>
-    <t>TTL:{{termsTTL}}</t>
-  </si>
-  <si>
-    <t xml:space="preserve">USD:{{termsUSD}} </t>
+    <t>TTL: PAIRS</t>
+  </si>
+  <si>
+    <t>{termsTTL}}</t>
+  </si>
+  <si>
+    <t>TTL USD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">{{termsUSD}} </t>
   </si>
   <si>
     <t>CONDITIONS</t>
@@ -1870,7 +1876,7 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="4" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="4" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -2569,10 +2575,10 @@
       <c r="G10" s="65" t="s">
         <v>43</v>
       </c>
-      <c r="H10" s="66"/>
-      <c r="I10" s="65" t="s">
+      <c r="H10" s="66" t="s">
         <v>44</v>
       </c>
+      <c r="I10" s="65"/>
       <c r="J10" s="67" t="s">
         <v>45</v>
       </c>
@@ -2581,17 +2587,21 @@
     </row>
     <row r="11" ht="22.5" customHeight="1" spans="1:13">
       <c r="A11" s="47"/>
-      <c r="B11" s="68"/>
+      <c r="B11" s="68" t="s">
+        <v>46</v>
+      </c>
       <c r="C11" s="68"/>
       <c r="D11" s="68"/>
       <c r="E11" s="68"/>
       <c r="F11" s="68"/>
       <c r="G11" s="69" t="s">
-        <v>46</v>
-      </c>
-      <c r="H11" s="69"/>
+        <v>47</v>
+      </c>
+      <c r="H11" s="69" t="s">
+        <v>48</v>
+      </c>
       <c r="I11" s="70" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="J11" s="71"/>
       <c r="K11" s="45"/>
@@ -2599,14 +2609,14 @@
     </row>
     <row r="12" ht="39.75" customHeight="1" spans="1:13">
       <c r="A12" s="29" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="B12" s="72" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="C12" s="73"/>
       <c r="D12" s="74" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="E12" s="74"/>
       <c r="F12" s="74"/>
@@ -2620,11 +2630,11 @@
     <row r="13" ht="22.5" customHeight="1" spans="1:13">
       <c r="A13" s="37"/>
       <c r="B13" s="76" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="C13" s="77"/>
       <c r="D13" s="78" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="E13" s="78"/>
       <c r="F13" s="78"/>
@@ -2638,11 +2648,11 @@
     <row r="14" ht="22.5" customHeight="1" spans="1:13">
       <c r="A14" s="37"/>
       <c r="B14" s="76" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="C14" s="77"/>
       <c r="D14" s="78" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="E14" s="78"/>
       <c r="F14" s="78"/>
@@ -2657,11 +2667,11 @@
     <row r="15" ht="26" customHeight="1" spans="1:13">
       <c r="A15" s="37"/>
       <c r="B15" s="76" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="C15" s="77"/>
       <c r="D15" s="78" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="E15" s="78"/>
       <c r="F15" s="78"/>
@@ -2675,11 +2685,11 @@
     <row r="16" ht="34.5" customHeight="1" spans="1:13">
       <c r="A16" s="47"/>
       <c r="B16" s="81" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="C16" s="82"/>
       <c r="D16" s="83" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="E16" s="83"/>
       <c r="F16" s="83"/>
@@ -2693,14 +2703,14 @@
     </row>
     <row r="17" ht="22.5" customHeight="1" spans="1:13">
       <c r="A17" s="29" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="B17" s="72" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="C17" s="73"/>
       <c r="D17" s="16" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="E17" s="16"/>
       <c r="F17" s="16"/>
@@ -2714,11 +2724,11 @@
     <row r="18" ht="22.5" customHeight="1" spans="1:13">
       <c r="A18" s="37"/>
       <c r="B18" s="76" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="C18" s="77"/>
       <c r="D18" s="78" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="E18" s="78"/>
       <c r="F18" s="78"/>
@@ -2732,11 +2742,11 @@
     <row r="19" ht="22.5" customHeight="1" spans="1:13">
       <c r="A19" s="37"/>
       <c r="B19" s="76" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="C19" s="77"/>
       <c r="D19" s="78" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="E19" s="78"/>
       <c r="F19" s="78"/>
@@ -2750,11 +2760,11 @@
     <row r="20" ht="22.5" customHeight="1" spans="1:13">
       <c r="A20" s="47"/>
       <c r="B20" s="85" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="C20" s="82"/>
       <c r="D20" s="83" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="E20" s="83"/>
       <c r="F20" s="83"/>
@@ -2767,20 +2777,20 @@
     </row>
     <row r="21" ht="18" spans="1:13">
       <c r="A21" s="29" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="B21" s="86" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="C21" s="87" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="D21" s="87"/>
       <c r="E21" s="87"/>
       <c r="F21" s="87"/>
       <c r="G21" s="87"/>
       <c r="H21" s="88" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="I21" s="89" t="s">
         <v>2</v>
@@ -2792,7 +2802,7 @@
     <row r="22" ht="33.75" spans="1:13">
       <c r="A22" s="91"/>
       <c r="B22" s="92" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="C22" s="93" t="s">
         <v>21</v>
@@ -2802,10 +2812,10 @@
       <c r="F22" s="94"/>
       <c r="G22" s="92"/>
       <c r="H22" s="94" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="I22" s="95" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="J22" s="96"/>
       <c r="K22" s="97"/>
@@ -2813,7 +2823,7 @@
     </row>
     <row r="23" ht="36.75" customHeight="1" spans="1:13">
       <c r="A23" s="99" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="B23" s="100"/>
       <c r="C23" s="100"/>
@@ -2849,7 +2859,7 @@
     </row>
     <row r="34" ht="15" spans="4:10">
       <c r="D34" s="1" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="H34" s="103"/>
       <c r="I34" s="103"/>

--- a/apps/web/server/modules/inquiry/excelTemplate/inquiry.xlsx
+++ b/apps/web/server/modules/inquiry/excelTemplate/inquiry.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="78">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="77">
   <si>
     <t>SUPPLIER:</t>
   </si>
@@ -140,7 +140,7 @@
     <t>PRODUCT DESCRIPTION</t>
   </si>
   <si>
-    <t>PAIRS</t>
+    <t>{{termsUnits1}}</t>
   </si>
   <si>
     <t>USD/PAIR</t>
@@ -152,36 +152,13 @@
     <t>REMARK</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <rFont val="微软雅黑"/>
-        <charset val="134"/>
-      </rPr>
-      <t>{{</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="微软雅黑"/>
-        <charset val="134"/>
-      </rPr>
-      <t>termsCode1</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <rFont val="微软雅黑"/>
-        <charset val="134"/>
-      </rPr>
-      <t>}}</t>
-    </r>
+    <t>{{termsCode1}}</t>
   </si>
   <si>
     <t>{{termsDesc1}}</t>
   </si>
   <si>
-    <t>{{termsUnits1}}</t>
+    <t>{{termsTTL}}</t>
   </si>
   <si>
     <t>{{termsUsd1}}</t>
@@ -193,10 +170,7 @@
     <t>TTL: PAIRS</t>
   </si>
   <si>
-    <t>{termsTTL}}</t>
-  </si>
-  <si>
-    <t>TTL USD</t>
+    <t>TTL USD:</t>
   </si>
   <si>
     <t xml:space="preserve">{{termsUSD}} </t>
@@ -387,6 +361,11 @@
       <charset val="134"/>
     </font>
     <font>
+      <sz val="9"/>
+      <name val="微软雅黑"/>
+      <charset val="134"/>
+    </font>
+    <font>
       <sz val="10"/>
       <name val="Microsoft YaHei"/>
       <charset val="134"/>
@@ -556,11 +535,6 @@
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <sz val="10"/>
-      <name val="微软雅黑"/>
-      <charset val="134"/>
-    </font>
   </fonts>
   <fills count="34">
     <fill>
@@ -1544,137 +1518,137 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="53" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="54" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="25" fillId="0" borderId="54" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="55" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="6" borderId="56" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="7" borderId="57" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="7" borderId="56" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="8" borderId="58" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="0" borderId="59" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="60" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="34" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="35" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="37" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="37" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="37" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="37" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="37" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="37" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="37" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="37" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="37" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="37" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="37" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="37" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="54" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="55" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="6" borderId="56" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="7" borderId="57" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="7" borderId="56" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="8" borderId="58" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="59" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="60" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="105">
+  <cellXfs count="106">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -1854,7 +1828,7 @@
     <xf numFmtId="0" fontId="11" fillId="3" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="3" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1879,10 +1853,13 @@
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="4" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="4" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="4" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -1927,37 +1904,37 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1966,22 +1943,22 @@
     <xf numFmtId="0" fontId="12" fillId="0" borderId="48" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="50" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="50" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="51" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="51" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="52" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -2561,7 +2538,7 @@
       <c r="K9" s="45"/>
       <c r="L9" s="46"/>
     </row>
-    <row r="10" ht="51.75" spans="1:13">
+    <row r="10" ht="36" spans="1:13">
       <c r="A10" s="37"/>
       <c r="B10" s="61" t="s">
         <v>41</v>
@@ -2595,122 +2572,122 @@
       <c r="E11" s="68"/>
       <c r="F11" s="68"/>
       <c r="G11" s="69" t="s">
+        <v>43</v>
+      </c>
+      <c r="H11" s="70" t="s">
         <v>47</v>
       </c>
-      <c r="H11" s="69" t="s">
+      <c r="I11" s="71" t="s">
         <v>48</v>
       </c>
-      <c r="I11" s="70" t="s">
-        <v>49</v>
-      </c>
-      <c r="J11" s="71"/>
+      <c r="J11" s="72"/>
       <c r="K11" s="45"/>
       <c r="L11" s="46"/>
     </row>
     <row r="12" ht="39.75" customHeight="1" spans="1:13">
       <c r="A12" s="29" t="s">
+        <v>49</v>
+      </c>
+      <c r="B12" s="73" t="s">
         <v>50</v>
       </c>
-      <c r="B12" s="72" t="s">
+      <c r="C12" s="74"/>
+      <c r="D12" s="75" t="s">
         <v>51</v>
       </c>
-      <c r="C12" s="73"/>
-      <c r="D12" s="74" t="s">
-        <v>52</v>
-      </c>
-      <c r="E12" s="74"/>
-      <c r="F12" s="74"/>
-      <c r="G12" s="74"/>
-      <c r="H12" s="74"/>
-      <c r="I12" s="74"/>
-      <c r="J12" s="75"/>
+      <c r="E12" s="75"/>
+      <c r="F12" s="75"/>
+      <c r="G12" s="75"/>
+      <c r="H12" s="75"/>
+      <c r="I12" s="75"/>
+      <c r="J12" s="76"/>
       <c r="K12" s="45"/>
       <c r="L12" s="46"/>
     </row>
     <row r="13" ht="22.5" customHeight="1" spans="1:13">
       <c r="A13" s="37"/>
-      <c r="B13" s="76" t="s">
+      <c r="B13" s="77" t="s">
+        <v>52</v>
+      </c>
+      <c r="C13" s="78"/>
+      <c r="D13" s="79" t="s">
         <v>53</v>
       </c>
-      <c r="C13" s="77"/>
-      <c r="D13" s="78" t="s">
-        <v>54</v>
-      </c>
-      <c r="E13" s="78"/>
-      <c r="F13" s="78"/>
-      <c r="G13" s="78"/>
-      <c r="H13" s="78"/>
-      <c r="I13" s="78"/>
-      <c r="J13" s="79"/>
+      <c r="E13" s="79"/>
+      <c r="F13" s="79"/>
+      <c r="G13" s="79"/>
+      <c r="H13" s="79"/>
+      <c r="I13" s="79"/>
+      <c r="J13" s="80"/>
       <c r="K13" s="45"/>
       <c r="L13" s="46"/>
     </row>
     <row r="14" ht="22.5" customHeight="1" spans="1:13">
       <c r="A14" s="37"/>
-      <c r="B14" s="76" t="s">
+      <c r="B14" s="77" t="s">
+        <v>54</v>
+      </c>
+      <c r="C14" s="78"/>
+      <c r="D14" s="79" t="s">
         <v>55</v>
       </c>
-      <c r="C14" s="77"/>
-      <c r="D14" s="78" t="s">
-        <v>56</v>
-      </c>
-      <c r="E14" s="78"/>
-      <c r="F14" s="78"/>
-      <c r="G14" s="78"/>
-      <c r="H14" s="78"/>
-      <c r="I14" s="78"/>
-      <c r="J14" s="79"/>
+      <c r="E14" s="79"/>
+      <c r="F14" s="79"/>
+      <c r="G14" s="79"/>
+      <c r="H14" s="79"/>
+      <c r="I14" s="79"/>
+      <c r="J14" s="80"/>
       <c r="K14" s="45"/>
       <c r="L14" s="46"/>
-      <c r="M14" s="80"/>
+      <c r="M14" s="81"/>
     </row>
     <row r="15" ht="26" customHeight="1" spans="1:13">
       <c r="A15" s="37"/>
-      <c r="B15" s="76" t="s">
+      <c r="B15" s="77" t="s">
+        <v>56</v>
+      </c>
+      <c r="C15" s="78"/>
+      <c r="D15" s="79" t="s">
         <v>57</v>
       </c>
-      <c r="C15" s="77"/>
-      <c r="D15" s="78" t="s">
-        <v>58</v>
-      </c>
-      <c r="E15" s="78"/>
-      <c r="F15" s="78"/>
-      <c r="G15" s="78"/>
-      <c r="H15" s="78"/>
-      <c r="I15" s="78"/>
-      <c r="J15" s="79"/>
+      <c r="E15" s="79"/>
+      <c r="F15" s="79"/>
+      <c r="G15" s="79"/>
+      <c r="H15" s="79"/>
+      <c r="I15" s="79"/>
+      <c r="J15" s="80"/>
       <c r="K15" s="45"/>
       <c r="L15" s="46"/>
     </row>
     <row r="16" ht="34.5" customHeight="1" spans="1:13">
       <c r="A16" s="47"/>
-      <c r="B16" s="81" t="s">
+      <c r="B16" s="82" t="s">
+        <v>58</v>
+      </c>
+      <c r="C16" s="83"/>
+      <c r="D16" s="84" t="s">
         <v>59</v>
       </c>
-      <c r="C16" s="82"/>
-      <c r="D16" s="83" t="s">
-        <v>60</v>
-      </c>
-      <c r="E16" s="83"/>
-      <c r="F16" s="83"/>
-      <c r="G16" s="83"/>
-      <c r="H16" s="83"/>
-      <c r="I16" s="83"/>
-      <c r="J16" s="84"/>
+      <c r="E16" s="84"/>
+      <c r="F16" s="84"/>
+      <c r="G16" s="84"/>
+      <c r="H16" s="84"/>
+      <c r="I16" s="84"/>
+      <c r="J16" s="85"/>
       <c r="K16" s="45"/>
       <c r="L16" s="46"/>
-      <c r="M16" s="80"/>
+      <c r="M16" s="81"/>
     </row>
     <row r="17" ht="22.5" customHeight="1" spans="1:13">
       <c r="A17" s="29" t="s">
+        <v>60</v>
+      </c>
+      <c r="B17" s="73" t="s">
         <v>61</v>
       </c>
-      <c r="B17" s="72" t="s">
+      <c r="C17" s="74"/>
+      <c r="D17" s="16" t="s">
         <v>62</v>
-      </c>
-      <c r="C17" s="73"/>
-      <c r="D17" s="16" t="s">
-        <v>63</v>
       </c>
       <c r="E17" s="16"/>
       <c r="F17" s="16"/>
@@ -2723,147 +2700,147 @@
     </row>
     <row r="18" ht="22.5" customHeight="1" spans="1:13">
       <c r="A18" s="37"/>
-      <c r="B18" s="76" t="s">
+      <c r="B18" s="77" t="s">
+        <v>63</v>
+      </c>
+      <c r="C18" s="78"/>
+      <c r="D18" s="79" t="s">
         <v>64</v>
       </c>
-      <c r="C18" s="77"/>
-      <c r="D18" s="78" t="s">
-        <v>65</v>
-      </c>
-      <c r="E18" s="78"/>
-      <c r="F18" s="78"/>
-      <c r="G18" s="78"/>
-      <c r="H18" s="78"/>
-      <c r="I18" s="78"/>
-      <c r="J18" s="79"/>
+      <c r="E18" s="79"/>
+      <c r="F18" s="79"/>
+      <c r="G18" s="79"/>
+      <c r="H18" s="79"/>
+      <c r="I18" s="79"/>
+      <c r="J18" s="80"/>
       <c r="K18" s="45"/>
       <c r="L18" s="46"/>
     </row>
     <row r="19" ht="22.5" customHeight="1" spans="1:13">
       <c r="A19" s="37"/>
-      <c r="B19" s="76" t="s">
+      <c r="B19" s="77" t="s">
+        <v>65</v>
+      </c>
+      <c r="C19" s="78"/>
+      <c r="D19" s="79" t="s">
         <v>66</v>
       </c>
-      <c r="C19" s="77"/>
-      <c r="D19" s="78" t="s">
-        <v>67</v>
-      </c>
-      <c r="E19" s="78"/>
-      <c r="F19" s="78"/>
-      <c r="G19" s="78"/>
-      <c r="H19" s="78"/>
-      <c r="I19" s="78"/>
-      <c r="J19" s="79"/>
+      <c r="E19" s="79"/>
+      <c r="F19" s="79"/>
+      <c r="G19" s="79"/>
+      <c r="H19" s="79"/>
+      <c r="I19" s="79"/>
+      <c r="J19" s="80"/>
       <c r="K19" s="45"/>
       <c r="L19" s="46"/>
     </row>
     <row r="20" ht="22.5" customHeight="1" spans="1:13">
       <c r="A20" s="47"/>
-      <c r="B20" s="85" t="s">
+      <c r="B20" s="86" t="s">
+        <v>67</v>
+      </c>
+      <c r="C20" s="83"/>
+      <c r="D20" s="84" t="s">
         <v>68</v>
       </c>
-      <c r="C20" s="82"/>
-      <c r="D20" s="83" t="s">
-        <v>69</v>
-      </c>
-      <c r="E20" s="83"/>
-      <c r="F20" s="83"/>
-      <c r="G20" s="83"/>
-      <c r="H20" s="83"/>
-      <c r="I20" s="83"/>
-      <c r="J20" s="84"/>
+      <c r="E20" s="84"/>
+      <c r="F20" s="84"/>
+      <c r="G20" s="84"/>
+      <c r="H20" s="84"/>
+      <c r="I20" s="84"/>
+      <c r="J20" s="85"/>
       <c r="K20" s="45"/>
       <c r="L20" s="46"/>
     </row>
     <row r="21" ht="18" spans="1:13">
       <c r="A21" s="29" t="s">
+        <v>69</v>
+      </c>
+      <c r="B21" s="87" t="s">
         <v>70</v>
       </c>
-      <c r="B21" s="86" t="s">
+      <c r="C21" s="88" t="s">
         <v>71</v>
       </c>
-      <c r="C21" s="87" t="s">
+      <c r="D21" s="88"/>
+      <c r="E21" s="88"/>
+      <c r="F21" s="88"/>
+      <c r="G21" s="88"/>
+      <c r="H21" s="89" t="s">
         <v>72</v>
       </c>
-      <c r="D21" s="87"/>
-      <c r="E21" s="87"/>
-      <c r="F21" s="87"/>
-      <c r="G21" s="87"/>
-      <c r="H21" s="88" t="s">
-        <v>73</v>
-      </c>
-      <c r="I21" s="89" t="s">
+      <c r="I21" s="90" t="s">
         <v>2</v>
       </c>
-      <c r="J21" s="90"/>
+      <c r="J21" s="91"/>
       <c r="K21" s="45"/>
       <c r="L21" s="46"/>
     </row>
     <row r="22" ht="33.75" spans="1:13">
-      <c r="A22" s="91"/>
-      <c r="B22" s="92" t="s">
+      <c r="A22" s="92"/>
+      <c r="B22" s="93" t="s">
+        <v>73</v>
+      </c>
+      <c r="C22" s="94" t="s">
+        <v>21</v>
+      </c>
+      <c r="D22" s="95"/>
+      <c r="E22" s="95"/>
+      <c r="F22" s="95"/>
+      <c r="G22" s="93"/>
+      <c r="H22" s="95" t="s">
+        <v>73</v>
+      </c>
+      <c r="I22" s="96" t="s">
         <v>74</v>
       </c>
-      <c r="C22" s="93" t="s">
-        <v>21</v>
-      </c>
-      <c r="D22" s="94"/>
-      <c r="E22" s="94"/>
-      <c r="F22" s="94"/>
-      <c r="G22" s="92"/>
-      <c r="H22" s="94" t="s">
-        <v>74</v>
-      </c>
-      <c r="I22" s="95" t="s">
-        <v>75</v>
-      </c>
-      <c r="J22" s="96"/>
-      <c r="K22" s="97"/>
-      <c r="L22" s="98"/>
+      <c r="J22" s="97"/>
+      <c r="K22" s="98"/>
+      <c r="L22" s="99"/>
     </row>
     <row r="23" ht="36.75" customHeight="1" spans="1:13">
-      <c r="A23" s="99" t="s">
-        <v>76</v>
-      </c>
-      <c r="B23" s="100"/>
-      <c r="C23" s="100"/>
-      <c r="D23" s="100"/>
-      <c r="E23" s="100"/>
-      <c r="F23" s="100"/>
-      <c r="G23" s="100"/>
-      <c r="H23" s="100"/>
-      <c r="I23" s="100"/>
-      <c r="J23" s="100"/>
-      <c r="K23" s="100"/>
-      <c r="L23" s="101"/>
+      <c r="A23" s="100" t="s">
+        <v>75</v>
+      </c>
+      <c r="B23" s="101"/>
+      <c r="C23" s="101"/>
+      <c r="D23" s="101"/>
+      <c r="E23" s="101"/>
+      <c r="F23" s="101"/>
+      <c r="G23" s="101"/>
+      <c r="H23" s="101"/>
+      <c r="I23" s="101"/>
+      <c r="J23" s="101"/>
+      <c r="K23" s="101"/>
+      <c r="L23" s="102"/>
     </row>
     <row r="24" ht="15.75" spans="1:13">
-      <c r="D24" s="102"/>
-      <c r="H24" s="103"/>
-      <c r="I24" s="103"/>
-      <c r="J24" s="103"/>
-      <c r="M24" s="104"/>
+      <c r="D24" s="103"/>
+      <c r="H24" s="104"/>
+      <c r="I24" s="104"/>
+      <c r="J24" s="104"/>
+      <c r="M24" s="105"/>
     </row>
     <row r="25" ht="13.5" spans="1:13">
-      <c r="M25" s="104"/>
+      <c r="M25" s="105"/>
     </row>
     <row r="32" ht="14.25" spans="1:13">
-      <c r="H32" s="103"/>
-      <c r="I32" s="103"/>
-      <c r="J32" s="103"/>
+      <c r="H32" s="104"/>
+      <c r="I32" s="104"/>
+      <c r="J32" s="104"/>
     </row>
     <row r="33" ht="14.25" spans="4:10">
-      <c r="H33" s="103"/>
-      <c r="I33" s="103"/>
-      <c r="J33" s="103"/>
+      <c r="H33" s="104"/>
+      <c r="I33" s="104"/>
+      <c r="J33" s="104"/>
     </row>
     <row r="34" ht="15" spans="4:10">
       <c r="D34" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="H34" s="103"/>
-      <c r="I34" s="103"/>
-      <c r="J34" s="103"/>
+        <v>76</v>
+      </c>
+      <c r="H34" s="104"/>
+      <c r="I34" s="104"/>
+      <c r="J34" s="104"/>
     </row>
   </sheetData>
   <mergeCells count="50">
